--- a/results/Int All Data -0.1/Rando_fi_explain.xlsx
+++ b/results/Int All Data -0.1/Rando_fi_explain.xlsx
@@ -1676,466 +1676,466 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007921895892264242</v>
+        <v>0.002281721694672132</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0001631474318729609</v>
+        <v>0.0005771625019066451</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005473987453161133</v>
+        <v>-0.000124103113996552</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0001727351011706968</v>
+        <v>-2.785160530260678e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.000102120978428587</v>
+        <v>-1.877927533898483e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001801048782643545</v>
+        <v>0.00178553719078508</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0003586126424018122</v>
+        <v>0.0002399026107667291</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001287679686426194</v>
+        <v>0.0009448768797186367</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001172989724176054</v>
+        <v>0.001341528903822806</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0001412113185804964</v>
+        <v>0.0002561677797624806</v>
       </c>
       <c r="L3" t="n">
-        <v>-9.058650551600379e-05</v>
+        <v>-0.0001720063708520225</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0004907688315929027</v>
+        <v>-3.732305278874907e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.005292688000841249</v>
+        <v>0.003947044996652083</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000525771853225211</v>
+        <v>0.0007087651787547899</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001112695585100207</v>
+        <v>-1.360187993809216e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002498035599209185</v>
+        <v>0.003611587657570936</v>
       </c>
       <c r="R3" t="n">
-        <v>5.862431171351208e-05</v>
+        <v>0.0003651141950372916</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008059657950019184</v>
+        <v>-8.417570870584818e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.000219885511999488</v>
+        <v>-0.000304254885991232</v>
       </c>
       <c r="U3" t="n">
-        <v>9.114907548341214e-05</v>
+        <v>0.001024744582115099</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001910473765093309</v>
+        <v>0.0009315809240725781</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00163312167443199</v>
+        <v>-0.0001874390354490752</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003782079402871095</v>
+        <v>0.000868628777041789</v>
       </c>
       <c r="Y3" t="n">
-        <v>-9.179034968159754e-06</v>
+        <v>0.000446310419069491</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.002281473209361262</v>
+        <v>0.003535363504494968</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.006331221371209751</v>
+        <v>0.007310135524035167</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0001195912995479464</v>
+        <v>0.0005872005962792781</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.0003978320092521615</v>
+        <v>0.001439433442635209</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.008364033279561919</v>
+        <v>0.00545541152799476</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.006683964083272986</v>
+        <v>0.005441630916826956</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.001462149550027732</v>
+        <v>0.0005623010645140634</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0003372248145631795</v>
+        <v>-0.0001783844783722755</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.0001039031802927637</v>
+        <v>-0.0001716973483677498</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0002770173585713742</v>
+        <v>0.002218071747686371</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.002703342713455719</v>
+        <v>0.0005539710368601106</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.01043452272893424</v>
+        <v>0.01120257902178057</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0001706202567988646</v>
+        <v>0.0001993399233580916</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.005367433936261174</v>
+        <v>0.003244111747831049</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.001239704190707168</v>
+        <v>0.001007518508733624</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.001264898112248915</v>
+        <v>-0.002201087911951913</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0002029830825019163</v>
+        <v>0.0002811224906301812</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.002062812380269307</v>
+        <v>0.001201787629872266</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.006520178153265345</v>
+        <v>0.004178855951489933</v>
       </c>
       <c r="AS3" t="n">
-        <v>-3.385659911919749e-05</v>
+        <v>0.001129281134496481</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.692028592491738e-05</v>
+        <v>-0.0008872849874444888</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.0004869899326966687</v>
+        <v>0.0001290924387412729</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.0003654509991242361</v>
+        <v>-0.0007335760150122695</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.213847534374043e-06</v>
+        <v>0.0005169435446115433</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0001564950248726681</v>
+        <v>4.777383195323839e-05</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.0009415178245602106</v>
+        <v>-1.524618521053676e-05</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.002440530265758334</v>
+        <v>0.0008500603162564001</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.00124956424978752</v>
+        <v>0.002025811600690036</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.006911135356811727</v>
+        <v>0.004647357166166961</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.000314355927868717</v>
+        <v>-5.915435547984021e-06</v>
       </c>
       <c r="BD3" t="n">
-        <v>-4.375950461776522e-05</v>
+        <v>0.0004903133207131361</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.0004483162499041693</v>
+        <v>8.110878985050581e-05</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.001786953822040736</v>
+        <v>0.002589964547237437</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.000499353757608817</v>
+        <v>-0.0004066299050302467</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.0002938803033073556</v>
+        <v>0.0007434299919565101</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.00296668789261016</v>
+        <v>0.002315535419392065</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0003879438122427314</v>
+        <v>0.0006646405358147177</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.599690928785091e-05</v>
+        <v>0.0005400390669971778</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.0001181560022512807</v>
+        <v>0.0007042699424996256</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.001044151491202047</v>
+        <v>0.0008751470825471008</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.001946030747412912</v>
+        <v>-0.0002331764200703944</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.0001351598194412873</v>
+        <v>0.002156970288616355</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.0004516198982394825</v>
+        <v>0.001144706311679874</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0008057335840337687</v>
+        <v>0.002831385147307198</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.0003547455219307471</v>
+        <v>0.001193957659330991</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0007125306314413072</v>
+        <v>0.0009533212996966913</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.0007664405206028169</v>
+        <v>0.0007475648120672474</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.0005851553017658306</v>
+        <v>0.0005758217949855127</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.428188445731673e-05</v>
+        <v>8.02953558268249e-05</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.0001295594856608828</v>
+        <v>0.0005964817783641408</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.001553144983916719</v>
+        <v>-0.0005143753335521317</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.941613957542216e-05</v>
+        <v>-0.0007410923821298599</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0.0005370773970674624</v>
+        <v>-0.0001191911455005146</v>
       </c>
       <c r="CB3" t="n">
-        <v>6.598989495770313e-05</v>
+        <v>0.0005688636656406132</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.0006085461425147521</v>
+        <v>0.0008078276895423266</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.0007131089559114124</v>
+        <v>-0.001097187595678473</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.0001651729096319588</v>
+        <v>-0.0002709533780724138</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.0003494930195389855</v>
+        <v>3.934761456625198e-05</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.0002532894796081264</v>
+        <v>0.0007840004706427438</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0004824497245554049</v>
+        <v>0.0002911831921249874</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.0001686544640164167</v>
+        <v>0.0005611134411828478</v>
       </c>
       <c r="CJ3" t="n">
-        <v>4.479669193659608e-05</v>
+        <v>3.439800397538884e-06</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.0001847469758458453</v>
+        <v>-0.0001090672895422928</v>
       </c>
       <c r="CL3" t="n">
-        <v>-7.908542157539888e-05</v>
+        <v>0.0008722625723223975</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.0004147858067617349</v>
+        <v>0.0001788990589507</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.0001968007560704399</v>
+        <v>0.0001467568435740241</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.0003056324531196563</v>
+        <v>0.0003402825752240746</v>
       </c>
       <c r="CP3" t="n">
-        <v>5.182347242672081e-05</v>
+        <v>0.0002196341077370256</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.0007815200942869128</v>
+        <v>-8.713305059943058e-05</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.0001663758889825285</v>
+        <v>-0.0001080029695455253</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.632477085996795e-05</v>
+        <v>-0.0004607897822658701</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0.001121147582085991</v>
+        <v>-0.0008619494602774558</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.355813341517576e-05</v>
+        <v>3.413094123980277e-05</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.872257706948322e-05</v>
+        <v>5.242829514087945e-05</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.0004541875303228216</v>
+        <v>-0.0007089871997445563</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.0004414818883890448</v>
+        <v>5.581987673298087e-05</v>
       </c>
       <c r="CZ3" t="n">
-        <v>8.742251986043503e-05</v>
+        <v>-4.184553683382886e-05</v>
       </c>
       <c r="DA3" t="n">
-        <v>-5.921570762204232e-05</v>
+        <v>-2.070555168123933e-05</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0.0004790291811622549</v>
+        <v>0.0004098450516822739</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.0002572609257000979</v>
+        <v>0.0001103897257664732</v>
       </c>
       <c r="DD3" t="n">
-        <v>-0.0001449976378741036</v>
+        <v>0.0001104397440495897</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.0005010939259470904</v>
+        <v>0.0006619450288612939</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.0003511897618854786</v>
+        <v>-0.0007714685789777309</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0.0003881207288972754</v>
+        <v>-0.001004345823796934</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0.0002507095886947297</v>
+        <v>-0.0004702043579364823</v>
       </c>
       <c r="DI3" t="n">
-        <v>5.693278876569598e-06</v>
+        <v>-0.0003384167276718497</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-3.098194944066049e-05</v>
+        <v>0.0008706056560311703</v>
       </c>
       <c r="DK3" t="n">
-        <v>9.273954270729746e-05</v>
+        <v>-0.0006458357265891523</v>
       </c>
       <c r="DL3" t="n">
-        <v>-6.445790274347773e-05</v>
+        <v>-0.0001740967194844378</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.0001299250391752249</v>
+        <v>-8.155473828975973e-05</v>
       </c>
       <c r="DN3" t="n">
-        <v>3.051901374610083e-05</v>
+        <v>-6.451588660700174e-05</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.0004597416086739104</v>
+        <v>-0.0004304435926899519</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.000395256521342543</v>
+        <v>-0.0003393076925915995</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-2.148145706702971e-06</v>
+        <v>7.476388771565534e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.0001369822300593371</v>
+        <v>-0.0001495744108603225</v>
       </c>
       <c r="DS3" t="n">
-        <v>-5.139822724508969e-05</v>
+        <v>-0.0001175124655434245</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0.001402806626619256</v>
+        <v>-0.001426147944539924</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0.0001762347345364966</v>
+        <v>-0.0002450006114257886</v>
       </c>
       <c r="DV3" t="n">
-        <v>1.362703871824467e-05</v>
+        <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.0001032753547787157</v>
+        <v>0.0002515066565460777</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.000307269959641362</v>
+        <v>-0.000800945279776848</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.0002843875961342058</v>
+        <v>0.001024744540633114</v>
       </c>
       <c r="DZ3" t="n">
-        <v>-1.025424728069657e-05</v>
+        <v>0.0002328530280298868</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.0005033734831918988</v>
+        <v>0.0001369521893643</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.0005322120319720925</v>
+        <v>-0.001550274909744504</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.0002160228281054611</v>
+        <v>-0.0001112345167139384</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0.000283593350036423</v>
+        <v>-0.0002199432497791686</v>
       </c>
       <c r="EE3" t="n">
-        <v>3.496236194026614e-05</v>
+        <v>0.0001408379688781125</v>
       </c>
       <c r="EF3" t="n">
-        <v>4.324787833317244e-05</v>
+        <v>-0.0002401662915339609</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.0003971029704906093</v>
+        <v>0.0001007542947888186</v>
       </c>
       <c r="EH3" t="n">
-        <v>3.333807169643266e-05</v>
+        <v>-3.662169071791178e-05</v>
       </c>
       <c r="EI3" t="n">
-        <v>-6.951533956616409e-05</v>
+        <v>-0.0003211755754758727</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0001001596114771564</v>
+        <v>0.0002025876562817186</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.0004216899577009093</v>
+        <v>-0.0007668535494709005</v>
       </c>
       <c r="EL3" t="n">
-        <v>-1.128846645798931e-05</v>
+        <v>9.902047315729633e-06</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.0001143402372110003</v>
+        <v>0.0001270862258303695</v>
       </c>
       <c r="EN3" t="n">
-        <v>-0.0002791796698895255</v>
+        <v>3.171731896597363e-05</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.0001662645890296644</v>
+        <v>0.0002041734901428216</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.0001545600684697934</v>
+        <v>0.0004559900926647787</v>
       </c>
       <c r="ER3" t="n">
-        <v>-6.120319480773406e-05</v>
+        <v>0.0001037594757652905</v>
       </c>
       <c r="ES3" t="n">
-        <v>1.96054911780863e-05</v>
+        <v>-1.232841173586573e-05</v>
       </c>
       <c r="ET3" t="n">
-        <v>-3.64892873260836e-05</v>
+        <v>-0.0004322662733086735</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0.0004243532973061959</v>
+        <v>-0.001612301887641613</v>
       </c>
       <c r="EV3" t="n">
-        <v>5.963294132055319e-05</v>
+        <v>8.48481210222085e-05</v>
       </c>
       <c r="EW3" t="n">
-        <v>3.692866567205349e-05</v>
+        <v>-0.0002576311730332948</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.0002621436964631551</v>
+        <v>-0.0001382429161078036</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.0001420027774239152</v>
+        <v>-0.0001359882472205243</v>
       </c>
     </row>
     <row r="4">
@@ -2145,466 +2145,466 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003259516905546233</v>
+        <v>0.003825730733358604</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001029336187165778</v>
+        <v>0.002572521711550464</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001109128583849175</v>
+        <v>0.00149838752377724</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0009666651202775089</v>
+        <v>0.0005048141790606677</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0006054725375630045</v>
+        <v>0.0009133883811542394</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002249527477797491</v>
+        <v>0.003655971788787669</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003000502380398667</v>
+        <v>0.001215859126939734</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003501739696680919</v>
+        <v>0.002148123465353162</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004253191171962045</v>
+        <v>0.002573326954307454</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003538536686825667</v>
+        <v>0.0009138535056041454</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005979836544570431</v>
+        <v>0.0006249396995185706</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002193058046150832</v>
+        <v>0.002263101467102157</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007349576485699737</v>
+        <v>0.004586921088495992</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00264707818481279</v>
+        <v>0.00338724454385341</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001503470528991602</v>
+        <v>0.001104411397758432</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007308693586292086</v>
+        <v>0.008526558418253538</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001401712118884284</v>
+        <v>0.001876542698995318</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003460998296467164</v>
+        <v>0.003536434341521582</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007671520937753825</v>
+        <v>0.0007242338835246954</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002107191506919705</v>
+        <v>0.001569076241041614</v>
       </c>
       <c r="V4" t="n">
-        <v>0.003472829730881364</v>
+        <v>0.001983007400364617</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002371425603378073</v>
+        <v>0.002625284062176538</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0112961905853632</v>
+        <v>0.00547305235297029</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0002905105960145183</v>
+        <v>0.0008562650736263121</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002084145853064174</v>
+        <v>0.004808200408210404</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.008053239571239408</v>
+        <v>0.007608139198066527</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001323840020913303</v>
+        <v>0.0009795821061997208</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.002603846800641337</v>
+        <v>0.001787171366761014</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.008003420042497628</v>
+        <v>0.006801291753055837</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.005995487232336979</v>
+        <v>0.008321573192341152</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.004607135505003021</v>
+        <v>0.003832765973031568</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001433411953632136</v>
+        <v>0.00115609293348345</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.000879310132428024</v>
+        <v>0.001402221933223354</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.001433877971602567</v>
+        <v>0.003079842134230283</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.01106575367512298</v>
+        <v>0.009144270482164187</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01517573420106234</v>
+        <v>0.009726009694354663</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0008123647520527251</v>
+        <v>0.001981691041012938</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.006046439621206161</v>
+        <v>0.004561066907869095</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.002488154829867146</v>
+        <v>0.003224983666082109</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.004225981963587468</v>
+        <v>0.003790680555832022</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0006416753229325287</v>
+        <v>0.001062091464678374</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.002918557836236063</v>
+        <v>0.003180403492771445</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.007701603953762513</v>
+        <v>0.006184565268871515</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.001639449368559694</v>
+        <v>0.002828576540185195</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.001944874742197092</v>
+        <v>0.003200140639848256</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.0007518296232804419</v>
+        <v>0.00110037075458872</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.001806259252939863</v>
+        <v>0.003178641714529796</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.001316988416824388</v>
+        <v>0.001713941679023885</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0007735511761797027</v>
+        <v>0.0008188773384926315</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.002758762769304484</v>
+        <v>0.002480216088661617</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.007523311723497427</v>
+        <v>0.002887164492125911</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.007015218644573661</v>
+        <v>0.004698071633457084</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.01054604634279927</v>
+        <v>0.005610430833314421</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.000567700336627332</v>
+        <v>0.0002399954450391651</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0003998792103700126</v>
+        <v>0.00123657612148607</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.003065935354383996</v>
+        <v>0.002802451848718741</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.006064606853857506</v>
+        <v>0.005155474769578195</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.004551769610029855</v>
+        <v>0.002186950976332592</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.001204142663549902</v>
+        <v>0.001599215699565375</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.005291735618583755</v>
+        <v>0.005888398603774317</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.001790023129980845</v>
+        <v>0.00221249313086876</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.005702648172956674</v>
+        <v>0.002632959901677372</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0007851660254243514</v>
+        <v>0.001436200021220809</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.001748750322067001</v>
+        <v>0.001535538801611303</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.01012143427207656</v>
+        <v>0.006169321676891693</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.003468673524154208</v>
+        <v>0.003534396259994942</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.002614907309925339</v>
+        <v>0.001756595287868278</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.0013726732472474</v>
+        <v>0.004968083036758456</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.001716889328919327</v>
+        <v>0.001990635936649673</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001743843228329584</v>
+        <v>0.00132346721414514</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.001805311146657552</v>
+        <v>0.001761929043292627</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.001258448183170108</v>
+        <v>0.00125565709264565</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.871901980779963e-05</v>
+        <v>0.0001436237598303228</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.001659968435462133</v>
+        <v>0.001095447909688438</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.003651927582942969</v>
+        <v>0.002839372870870248</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.002560022057166431</v>
+        <v>0.004204680263412105</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.001457064569377926</v>
+        <v>0.001465880046688884</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.00091809185507934</v>
+        <v>0.001372589664948543</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.001683302411495193</v>
+        <v>0.001267027613125936</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.002060766760523796</v>
+        <v>0.002650949563409567</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.001675716604322662</v>
+        <v>0.001692352671602268</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.002103578363496776</v>
+        <v>0.002003098455219295</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.002405149310439468</v>
+        <v>0.00141802902984649</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0008429298531558583</v>
+        <v>0.001281256953009112</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.0007995843371864247</v>
+        <v>0.001894482819429239</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0001416595781605428</v>
+        <v>2.895422976971644e-05</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.00145034003867597</v>
+        <v>0.001030548322461123</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.001000921854001957</v>
+        <v>0.002640080562863084</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.0009498134449902334</v>
+        <v>0.0005665932177938777</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0005459666208253416</v>
+        <v>0.001134358795874705</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.000943951657095303</v>
+        <v>0.001171620902722237</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0001497430374579397</v>
+        <v>0.0003505058840745842</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.0009997105209529407</v>
+        <v>0.002222554502602476</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.002738408864413665</v>
+        <v>0.003669300401807257</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.001490554571904655</v>
+        <v>0.003104249242872338</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.001791438209262327</v>
+        <v>0.002852807035968223</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0003007075863524055</v>
+        <v>0.0004937144656139027</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0003427841242709199</v>
+        <v>0.000409958219038773</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.001344370040043556</v>
+        <v>0.001951624494647263</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.002015698674028213</v>
+        <v>0.002680975793013111</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0005591720421653193</v>
+        <v>0.0002359592776344271</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.000460915337533585</v>
+        <v>0.0003462816532337236</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.001142423250706526</v>
+        <v>0.001783562082610826</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.002764347050571271</v>
+        <v>0.001391257704635136</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0005911276724804657</v>
+        <v>0.0004434498390111973</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.001271389784815709</v>
+        <v>0.001695718303919175</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.001280108803965786</v>
+        <v>0.002508627218720023</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.001046873636335711</v>
+        <v>0.001869855891110004</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.002230276997172157</v>
+        <v>0.003183675366584429</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.001864524343262699</v>
+        <v>0.001391980508511569</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0008256285498811687</v>
+        <v>0.00273711607062361</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.001052477684009798</v>
+        <v>0.001813213842264756</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0001485482048315606</v>
+        <v>0.0003365002622419208</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.001434111120331768</v>
+        <v>0.001645318949143969</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.00294717381449181</v>
+        <v>0.002496086062173512</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.001575259267686722</v>
+        <v>0.002375341001402827</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.001829364556251697</v>
+        <v>0.002699860225398786</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0002416993022529965</v>
+        <v>0.0004682574173089045</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0003048996343435735</v>
+        <v>0.0002837055002102186</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0003426547999544278</v>
+        <v>0.000345741762854621</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.0023023220771966</v>
+        <v>0.00230991733812273</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.001662462095893309</v>
+        <v>0.001878318851017992</v>
       </c>
       <c r="DV4" t="n">
-        <v>2.873235237702227e-05</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.000194261147069007</v>
+        <v>0.0009590026408945071</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.002489601237559517</v>
+        <v>0.002626456766308947</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.002349319172375231</v>
+        <v>0.00294830689031679</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0005219969936835569</v>
+        <v>0.0002901361690811394</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.003266547949346374</v>
+        <v>0.002460434017751549</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.003427787772488206</v>
+        <v>0.003957047403439365</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.001502763639325358</v>
+        <v>0.001250424138938227</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.001349544114905617</v>
+        <v>0.001670884254320367</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0003635266878431935</v>
+        <v>0.0001938949522171657</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0007752434578956038</v>
+        <v>0.001394231245976137</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.001263923683313287</v>
+        <v>0.001204477328249799</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.000380405514786411</v>
+        <v>0.0005593075712985799</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.001151196531846096</v>
+        <v>0.002409979656924316</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.001193307877543012</v>
+        <v>0.001285205241996728</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.001637758129918796</v>
+        <v>0.004202523090885509</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0001130916981105793</v>
+        <v>7.483204389872426e-05</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0003289036642665983</v>
+        <v>0.0002645597082610276</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0002797630172391079</v>
+        <v>0.0003559551349315581</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0007502963488148472</v>
+        <v>0.0006116458120944541</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.001436354569391455</v>
+        <v>0.001036915118667457</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.0001146927349950833</v>
+        <v>0.0002890231476774221</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0001048945913872055</v>
+        <v>0.0001924983269500789</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.0006870657107764688</v>
+        <v>0.002445909743523672</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.00146490930422497</v>
+        <v>0.003582394859803256</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0003167806964558232</v>
+        <v>0.000346396762407331</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.001247931004407512</v>
+        <v>0.001189631810194292</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.00267124350221878</v>
+        <v>0.0008390439271464995</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0005379665933502777</v>
+        <v>0.000803630017228738</v>
       </c>
     </row>
     <row r="5">
@@ -2614,466 +2614,466 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.004944674965421836</v>
+        <v>-0.002845246356696785</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.001346469622331647</v>
+        <v>-0.003612479474548469</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.001018062397372732</v>
+        <v>-0.003743842364532035</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.001577181208053668</v>
+        <v>-0.001033769813921448</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0009715242881072284</v>
+        <v>-0.001241610738255006</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002776813606386708</v>
+        <v>-0.002814070351758768</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.005221300138312568</v>
+        <v>-0.001895244658855988</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.006535269709543545</v>
+        <v>-0.001860785665058606</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.005186721991701226</v>
+        <v>-0.0007261410788381717</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0006711409395973034</v>
+        <v>-0.000886699507389177</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.001083743842364515</v>
+        <v>-0.00172294968986908</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.004031702274293536</v>
+        <v>-0.004137931034482767</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.006777316735822936</v>
+        <v>0.0004165220409579895</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.003284923928077443</v>
+        <v>-0.005188834154351429</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.0006040268456375842</v>
+        <v>-0.001860785665058606</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.009581239530988295</v>
+        <v>-0.01460636515912896</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.001884816753926744</v>
+        <v>-0.00215203054494969</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.005394190871369275</v>
+        <v>-0.007512060647829078</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.00144727773948996</v>
+        <v>-0.001641541038525984</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.002177554438861018</v>
+        <v>-0.0009424083769634106</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.003699861687413541</v>
+        <v>-0.001457321304649584</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.001313628899835773</v>
+        <v>-0.004827586206896573</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.002266009852216721</v>
+        <v>-0.00958949096880134</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.0005033557046979498</v>
+        <v>-0.0009715242881072172</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.001255230125523032</v>
+        <v>-0.004476058292852259</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.0007983339118362353</v>
+        <v>-0.0001708817498291104</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.001619572708476835</v>
+        <v>-0.0007236388697450136</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.005117565698478543</v>
+        <v>-0.001172529313232851</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.003342522398345904</v>
+        <v>-0.006099241902136443</v>
       </c>
       <c r="AE5" t="n">
-        <v>6.437077566784355e-05</v>
+        <v>-0.004999999999999938</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.003517587939698508</v>
+        <v>-0.006867671691792277</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.001457827143353074</v>
+        <v>-0.002024432809773169</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.001757408683666384</v>
+        <v>-0.003608605135322751</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.002360291565428718</v>
+        <v>-0.001444991789819383</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.02265851303508208</v>
+        <v>-0.01741229481815256</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.0103400416377516</v>
+        <v>-0.001873698820263758</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.001071922544951587</v>
+        <v>-0.003809523809523829</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.0006891798759475765</v>
+        <v>-0.001273031825795645</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.001492537313432896</v>
+        <v>-0.003481116584564881</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.003284072249589443</v>
+        <v>-0.0105747126436782</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.001033769813921392</v>
+        <v>-0.001373534338358484</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.001707717569786504</v>
+        <v>-0.002953020134228124</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.004216285806243969</v>
+        <v>-0.006275167785234848</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.002894555478979943</v>
+        <v>-0.001576354679802972</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.004598893499308421</v>
+        <v>-0.006561954624781885</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.0004859423811177099</v>
+        <v>-0.001442953020134175</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.002101998621640189</v>
+        <v>-0.008866995073891659</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.002143845089903174</v>
+        <v>-0.001145435612634493</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.0008677542519959114</v>
+        <v>-0.001431064572425888</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.002731673582295979</v>
+        <v>-0.005259631490787264</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.005152143845089885</v>
+        <v>-0.004105090311986881</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.01455739972337478</v>
+        <v>-0.005061082024432862</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.002290871225269053</v>
+        <v>-0.002213001383125857</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.0002298850574712574</v>
+        <v>-0.0004510756419153439</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.0007718120805369155</v>
+        <v>-0.0009773123909250225</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.005739972337482691</v>
+        <v>-0.004203612479474561</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.008235699517574057</v>
+        <v>-0.003296321998612128</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.008955739972337451</v>
+        <v>-0.004198473282442805</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.001895244658855899</v>
+        <v>-0.0009773123909250004</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.003782095766828653</v>
+        <v>-0.00760469011725291</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.003350083752093813</v>
+        <v>-0.00247906197654939</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.01528354080221295</v>
+        <v>-0.00506108202443285</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.001550654720882094</v>
+        <v>-0.0007881773399015191</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.0011756569847856</v>
+        <v>-0.001711409395973074</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.01715076071922539</v>
+        <v>-0.01414246196403868</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.006409372846312866</v>
+        <v>-0.003054494967025367</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.007641770401106474</v>
+        <v>-0.0006942034015966492</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.0009715475364330484</v>
+        <v>-0.00194630872483218</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.00411479944674964</v>
+        <v>-0.001431064572425888</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.001516195727084724</v>
+        <v>-0.0004537521815009326</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.002221450885109388</v>
+        <v>-0.0006202618883528688</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.0005900728913571962</v>
+        <v>-0.0009424083769633884</v>
       </c>
       <c r="BW5" t="n">
-        <v>-1.110223024625157e-17</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.003596127247579517</v>
+        <v>-0.001442953020134163</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.005482303955586476</v>
+        <v>-0.005898681471200595</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.004823039555864062</v>
+        <v>-0.008223455933379632</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.00297372060857537</v>
+        <v>-0.00322804581742453</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.001486860304287674</v>
+        <v>-0.0009024644220756439</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.002117320374869891</v>
+        <v>-0.001033769813921448</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.004723618090452286</v>
+        <v>-0.006371100164203658</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.002364532019704402</v>
+        <v>-0.003066850447966951</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.005670816044260008</v>
+        <v>-0.004031702274293591</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.006016597510373423</v>
+        <v>-0.0009303928325293031</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.0006365159128978393</v>
+        <v>-0.001596113809854294</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.001244813278008283</v>
+        <v>-0.001873698820263736</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0</v>
+        <v>-3.355704697985962e-05</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.002082610204790059</v>
+        <v>-0.001735508503991667</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.001476510067114067</v>
+        <v>-0.001642036124794766</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0.0009731543624160955</v>
+        <v>-0.0009303928325293031</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.0003940886699507318</v>
+        <v>-0.001541038525963156</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0.001839080459770082</v>
+        <v>-0.001608040201005023</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.0001675041876046945</v>
+        <v>-0.0001367053998632795</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.0007553366174055665</v>
+        <v>-0.00479061976549412</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.005829145728643248</v>
+        <v>-0.008899835796387567</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.002742103436306875</v>
+        <v>-0.006633825944170812</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.00454858718125426</v>
+        <v>-0.007881773399014802</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0.0004512322110378552</v>
+        <v>-0.0004886561954625113</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0.0006700167504187782</v>
+        <v>-0.0005933682373473359</v>
       </c>
       <c r="CW5" t="n">
         <v>0</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0.001791867677463765</v>
+        <v>-0.003839441535776656</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.002857142857142825</v>
+        <v>-0.003513957307060778</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.000691562932226808</v>
+        <v>-0.000381811870878157</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0.00123953098827474</v>
+        <v>-0.0009852216748768793</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0.002316735822959881</v>
+        <v>-0.002814070351758757</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0.00368711233631972</v>
+        <v>-0.002067539627842896</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0.0009395973154362691</v>
+        <v>-0.0004135079255685792</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0.001208053691275146</v>
+        <v>-0.001206030150753767</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.002395001735508551</v>
+        <v>-0.007290640394088698</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0.002003284072249567</v>
+        <v>-0.005469798657718072</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.004479669193659497</v>
+        <v>-0.007717569786535328</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.003583735354927575</v>
+        <v>-0.002988505747126446</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.001585113714679476</v>
+        <v>-0.005754651964162627</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0.001826326671261147</v>
+        <v>-0.004858718125430717</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0.0003471017007983246</v>
+        <v>-0.0008959338387319216</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0.003135768435561626</v>
+        <v>-0.004169538249483096</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0.006431535269709521</v>
+        <v>-0.003776683087027921</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.003508207273897668</v>
+        <v>-0.004345027357579656</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0.002101806239737247</v>
+        <v>-0.007027914614121567</v>
       </c>
       <c r="DQ5" t="n">
+        <v>-0.0006980802792321495</v>
+      </c>
+      <c r="DR5" t="n">
         <v>-0.0005513439007581056</v>
       </c>
-      <c r="DR5" t="n">
-        <v>-0.0007580978635423951</v>
-      </c>
       <c r="DS5" t="n">
-        <v>-0.0003862246540070835</v>
+        <v>-0.0009852216748769127</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.005535886707434812</v>
+        <v>-0.005779967159277544</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0.004119729642742198</v>
+        <v>-0.004170771756978664</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0.0001735508503991734</v>
+        <v>-0.000361247947454868</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.005651274982770471</v>
+        <v>-0.007718814610613367</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0.003618194348724957</v>
+        <v>-0.003973727422003304</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.0008270158511371362</v>
+        <v>0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.009648518263266658</v>
+        <v>-0.006547208821502393</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.0091632088520055</v>
+        <v>-0.01024630541871924</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0.001659751037344392</v>
+        <v>-0.00303239145416957</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0.003618194348724957</v>
+        <v>-0.004203997243280499</v>
       </c>
       <c r="EE5" t="n">
-        <v>-0.0008690054715159267</v>
+        <v>0</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0.001396160558464254</v>
+        <v>-0.002894555478980032</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.003549276361130194</v>
+        <v>-0.00205933682373477</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0.000593368237347347</v>
+        <v>-0.001240523776705738</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.002349533311876428</v>
+        <v>-0.006409372846312866</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.002178423236514515</v>
+        <v>-0.002343211578221938</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0.003962784286698773</v>
+        <v>-0.01247415575465195</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0.0002443280977312834</v>
+        <v>-0.0001396160558464477</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0.0003818118708781903</v>
+        <v>-3.350083752093891e-05</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0.0007580978635423951</v>
+        <v>-0.0005254515599343535</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.00154103852596319</v>
+        <v>-0.0008538587848932911</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0.00348035837353543</v>
+        <v>-0.001291448516579485</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.0003101309441764344</v>
+        <v>-6.700167504187781e-05</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.0001340033500837556</v>
+        <v>-0.0003803596127247566</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0.00141281874569259</v>
+        <v>-0.007064093728463117</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.003859407305306628</v>
+        <v>-0.01154376292212268</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0.0006547208821502282</v>
+        <v>-0.0005704697986576912</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0.002317347924042501</v>
+        <v>-0.001700798333911835</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.007201929703652632</v>
+        <v>-0.001735508503991667</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.001516195727084724</v>
+        <v>-0.002200328407224983</v>
       </c>
     </row>
     <row r="6">
@@ -3083,466 +3083,466 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.0006295322972022677</v>
+        <v>-0.0003773951776156276</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0004286181737168687</v>
+        <v>-0.0002001418050739806</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.740884627657313e-05</v>
+        <v>-5.246562020525814e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.000532190690659376</v>
+        <v>-0.0002687082883878505</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0004954012289209081</v>
+        <v>-0.0007512934128772158</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0007993272967948218</v>
+        <v>-0.0003848843022010329</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0009634998728371702</v>
+        <v>-0.0003308957063636431</v>
       </c>
       <c r="I6" t="n">
-        <v>2.650462778059913e-05</v>
+        <v>-0.0005018183905287216</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0007462265034911597</v>
+        <v>-0.0002121468592948428</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0004568193160483763</v>
+        <v>-0.0001906251098071132</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.000532564390878093</v>
+        <v>-0.0002744705547099269</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0004559886624559334</v>
+        <v>-0.00134318214089055</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001569372772667246</v>
+        <v>0.001510172570410831</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.001032329476353388</v>
+        <v>-0.001032540242479804</v>
       </c>
       <c r="P6" t="n">
-        <v>-7.807078417767233e-05</v>
+        <v>-0.0004847468214947665</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0002430404422861271</v>
+        <v>0.00151784735955082</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.0009054904982404355</v>
+        <v>-0.0008461366837338141</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0004058840300857652</v>
+        <v>-0.001138191692011053</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0005735128914939574</v>
+        <v>-0.0007059339852545754</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.001146198613613036</v>
+        <v>-7.740494200411663e-06</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0001253744489350284</v>
+        <v>-0.0004838848339480506</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0003706568642285607</v>
+        <v>-0.001210466874262594</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.001611020754098144</v>
+        <v>-0.001475890764128088</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.0001033769813921448</v>
+        <v>3.417634996581987e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0005313597184425117</v>
+        <v>0.0002548027217426918</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001945423543845701</v>
+        <v>0.001462552731361943</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0009410467819835316</v>
+        <v>1.708817498290993e-05</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.001988507444613769</v>
+        <v>0.0002929011652225394</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.004540092393994388</v>
+        <v>0.001068064644511474</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.002771544226902031</v>
+        <v>-0.002320927711127358</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.001289815916862339</v>
+        <v>-0.0006136522064959598</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0007247149660120882</v>
+        <v>-0.0008743926385892387</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0007056244674680689</v>
+        <v>1.677852348993814e-05</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.000100502512562814</v>
+        <v>0.0002831559824745588</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.001344112740971498</v>
+        <v>-0.002753257255076705</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.004199166717767456</v>
+        <v>0.007303382273523823</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0003225229023517823</v>
+        <v>-0.0006618663788742291</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0009059207693869642</v>
+        <v>0.0003953598362173266</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.0002236301548935116</v>
+        <v>-0.0008163111383403838</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.0001331589595276433</v>
+        <v>-0.00381465145848566</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.516778523490582e-05</v>
+        <v>-0.0005021977942401195</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-4.987109323031924e-05</v>
+        <v>-0.0006379054825207703</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.002521404611499947</v>
+        <v>0.0003777008447558738</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.001029078066853137</v>
+        <v>-0.0007000321853878444</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.000110005497160906</v>
+        <v>-0.001834369932292912</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>-0.0003293713116935326</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.000947325183101705</v>
+        <v>-0.0008753642953153617</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.0008630119065826335</v>
+        <v>-0.0004271356783919711</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0003876938056456225</v>
+        <v>-0.0002422479246021486</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.001438789280546746</v>
+        <v>-0.001108374384236469</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.0008524361307378214</v>
+        <v>-0.0005459018115374275</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.0007633909291328983</v>
+        <v>-0.001110461395617671</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.0001699082363344178</v>
+        <v>0.0006254501415222129</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.675041876046945e-05</v>
+        <v>-0.0001047120418848524</v>
       </c>
       <c r="BD6" t="n">
-        <v>-2.593360995850058e-05</v>
+        <v>-0.0001070662549791462</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.0004916766102336711</v>
+        <v>-0.001824276698482402</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.001976279636265049</v>
+        <v>-0.001169700853772465</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.000910870979575945</v>
+        <v>-0.001988062392735362</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.0002529571792807911</v>
+        <v>-0.0001663068988244531</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.001020211708612192</v>
+        <v>-0.001695891207356456</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.0002610497848331117</v>
+        <v>-0.0004892264633254901</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.0001333663311884725</v>
+        <v>-0.0006482412313612851</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0001041214774055138</v>
+        <v>-5.892879880136647e-05</v>
       </c>
       <c r="BM6" t="n">
-        <v>-7.846211642919542e-05</v>
+        <v>6.945764070682425e-05</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.0004022364215736818</v>
+        <v>-0.001266815824850709</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.001142077018940491</v>
+        <v>-0.0002767256220521014</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.417634996582264e-05</v>
+        <v>-0.0001490863193181369</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.0003392248884494242</v>
+        <v>0.0003586843952060548</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.0005900578366338948</v>
+        <v>0.000165205333081922</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0003266331658291543</v>
+        <v>0.000344631170402479</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.0001537935748461783</v>
+        <v>-0.0003467716421270972</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.0004562283630258124</v>
+        <v>-9.597592453790271e-05</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.0005212781609575639</v>
+        <v>-3.461324813895106e-05</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.0008276258256422363</v>
+        <v>-0.002504018726578888</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.0007411289933411752</v>
+        <v>-0.00108978121689135</v>
       </c>
       <c r="CA6" t="n">
-        <v>-0.00131625704065875</v>
+        <v>-0.0005646434028908826</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.000303954794172509</v>
+        <v>-0.0006019847094131808</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.0001900897535487001</v>
+        <v>-0.0001061323356670307</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.002022938133296251</v>
+        <v>-0.001957859317838714</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0007546842470506714</v>
+        <v>-0.001305939831007932</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.0006783919597990101</v>
+        <v>-0.001149103720748854</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.0007590923177257902</v>
+        <v>-6.955379518816807e-05</v>
       </c>
       <c r="CH6" t="n">
-        <v>-9.047582052919558e-05</v>
+        <v>-0.0005528902903780636</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.0004291997070913711</v>
+        <v>-6.861763867748172e-05</v>
       </c>
       <c r="CJ6" t="n">
         <v>0</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.0004624905758120634</v>
+        <v>-0.0005604369142150511</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.0007756848188829379</v>
+        <v>-0.0004361372408449554</v>
       </c>
       <c r="CM6" t="n">
-        <v>-5.246562020525814e-05</v>
+        <v>-1.103279015632342e-05</v>
       </c>
       <c r="CN6" t="n">
-        <v>-9.205639249024178e-05</v>
+        <v>-0.0006453604262918411</v>
       </c>
       <c r="CO6" t="n">
-        <v>4.208448883627204e-05</v>
+        <v>-0.0001456133193526526</v>
       </c>
       <c r="CP6" t="n">
-        <v>-3.397995691698796e-05</v>
+        <v>3.251425025567189e-05</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0003162137356147315</v>
+        <v>-0.0006287301536329809</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.001351436046571469</v>
+        <v>-0.0007197739470168052</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0.0005902756653652419</v>
+        <v>-0.0006516977640347893</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0.001745341907315942</v>
+        <v>-0.001548469841005093</v>
       </c>
       <c r="CU6" t="n">
-        <v>-0.0001201548010819647</v>
+        <v>-0.0001812840887524758</v>
       </c>
       <c r="CV6" t="n">
-        <v>-3.470715913516942e-05</v>
+        <v>-0.0001459997502301053</v>
       </c>
       <c r="CW6" t="n">
         <v>0</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0.0003356838876542701</v>
+        <v>-0.001487455113665481</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0.001355298093455573</v>
+        <v>-0.001259978374425558</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.0001970443349753575</v>
+        <v>-0.0002453224167262708</v>
       </c>
       <c r="DA6" t="n">
-        <v>-9.451824392757991e-05</v>
+        <v>8.375209380234727e-06</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0.001194206494942166</v>
+        <v>0.0001369880436948412</v>
       </c>
       <c r="DC6" t="n">
-        <v>-0.002072876474522142</v>
+        <v>-0.0009518033517340596</v>
       </c>
       <c r="DD6" t="n">
-        <v>-0.0004707680397477237</v>
+        <v>-0.0001941414814440157</v>
       </c>
       <c r="DE6" t="n">
-        <v>-4.071699625237401e-05</v>
+        <v>-0.000490413666573758</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.001068409314030752</v>
+        <v>-0.0005361010988625792</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0.001063457977833512</v>
+        <v>-0.0009487915769322953</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.0010732984293194</v>
+        <v>-0.001191505406995022</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.0004402805539264421</v>
+        <v>-0.0006311228768456772</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.000130890052356053</v>
+        <v>0.0004491794290126638</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0.0003470715913517164</v>
+        <v>-0.00115074655670791</v>
       </c>
       <c r="DL6" t="n">
-        <v>-9.416347809463322e-05</v>
+        <v>-0.0003272376223007301</v>
       </c>
       <c r="DM6" t="n">
-        <v>-9.852216748769128e-05</v>
+        <v>-0.0003980637011902211</v>
       </c>
       <c r="DN6" t="n">
-        <v>3.417634996578933e-05</v>
+        <v>-0.001167908218841166</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.0009424644596162768</v>
+        <v>-0.00191967041645211</v>
       </c>
       <c r="DP6" t="n">
-        <v>-0.0008524046460422736</v>
+        <v>-0.0005251856850570058</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-9.852216748769128e-05</v>
+        <v>-8.256615719106353e-05</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.0002074036332970291</v>
+        <v>-0.000432812462873386</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.0003072941152423208</v>
+        <v>-0.0001931123270035639</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0.002033460261984837</v>
+        <v>-0.001995285593365378</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0.0004013641267827357</v>
+        <v>-0.001439165343605583</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
       </c>
       <c r="DW6" t="n">
+        <v>-0.0001716943536680004</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>-0.0009158172929462443</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>0.0001540373871182804</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>6.603960723378932e-05</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>6.035436043698717e-05</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>-0.00343013070723604</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>-0.0004869442908321586</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>-0.0008037666252218689</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>8.046346958481831e-06</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>-0.00104582848561364</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>-0.00021907089357312</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>-0.0002589241899107919</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>-0.0001493307198308369</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>-0.0001643908898769669</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>-0.0001128140746487843</v>
+      </c>
+      <c r="EL6" t="n">
         <v>0</v>
       </c>
-      <c r="DX6" t="n">
-        <v>6.06437800383719e-05</v>
-      </c>
-      <c r="DY6" t="n">
-        <v>-0.000694752513393393</v>
-      </c>
-      <c r="DZ6" t="n">
-        <v>-0.0002348009623059144</v>
-      </c>
-      <c r="EA6" t="n">
-        <v>4.241078596430026e-05</v>
-      </c>
-      <c r="EB6" t="n">
-        <v>-0.000697158675775944</v>
-      </c>
-      <c r="EC6" t="n">
-        <v>-0.0002886765518891499</v>
-      </c>
-      <c r="ED6" t="n">
-        <v>-0.0006193039429663067</v>
-      </c>
-      <c r="EE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF6" t="n">
-        <v>-6.885044046461841e-05</v>
-      </c>
-      <c r="EG6" t="n">
-        <v>-0.000561566573671815</v>
-      </c>
-      <c r="EH6" t="n">
-        <v>-2.56322624743649e-05</v>
-      </c>
-      <c r="EI6" t="n">
-        <v>-0.0006282722513089312</v>
-      </c>
-      <c r="EJ6" t="n">
-        <v>-0.0005004146584076912</v>
-      </c>
-      <c r="EK6" t="n">
-        <v>-0.001234143180306554</v>
-      </c>
-      <c r="EL6" t="n">
-        <v>-2.512562814070418e-05</v>
-      </c>
       <c r="EM6" t="n">
-        <v>-7.389162561576845e-05</v>
+        <v>8.046346958481831e-06</v>
       </c>
       <c r="EN6" t="n">
-        <v>-0.0004215052865112507</v>
+        <v>-0.0001178575976027329</v>
       </c>
       <c r="EO6" t="n">
         <v>0</v>
       </c>
       <c r="EP6" t="n">
+        <v>-0.0001832460732984542</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>-0.0001316967968510691</v>
+      </c>
+      <c r="ER6" t="n">
         <v>0</v>
       </c>
-      <c r="EQ6" t="n">
-        <v>-0.0003465911089090224</v>
-      </c>
-      <c r="ER6" t="n">
-        <v>-5.025125628140836e-05</v>
-      </c>
       <c r="ES6" t="n">
-        <v>0</v>
+        <v>-0.0001318787128500171</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.0003895130100766031</v>
+        <v>-0.0003364115516500621</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0.0004376061431376283</v>
+        <v>-0.001228635398858904</v>
       </c>
       <c r="EV6" t="n">
-        <v>-2.603262755987434e-05</v>
+        <v>-5.16884906960724e-05</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0.0005346167564242943</v>
+        <v>-0.001274347571856863</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0.0003123915307185143</v>
+        <v>-0.0006040236790089276</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.0002331011421423973</v>
+        <v>-0.0002192671095847199</v>
       </c>
     </row>
     <row r="7">
@@ -3552,442 +3552,442 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001705179178312088</v>
+        <v>0.001900759015868497</v>
       </c>
       <c r="C7" t="n">
-        <v>-3.490401396162301e-05</v>
+        <v>0.0001165774188784052</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0004143867605019502</v>
+        <v>0.0001838404509769575</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0001926997407846409</v>
+        <v>1.677852348995201e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0001510067114093794</v>
+        <v>5.178630128408468e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001605322031927298</v>
+        <v>0.0008825574069648624</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0003102722660922152</v>
+        <v>0.0002042658551053344</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001867600941416819</v>
+        <v>0.0009745016546392315</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0009259153068760851</v>
+        <v>0.0006889239063988695</v>
       </c>
       <c r="K7" t="n">
-        <v>2.512738467241871e-06</v>
+        <v>-1.413219157808676e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.497708013683875e-05</v>
+        <v>-1.735508503991623e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002089714223100725</v>
+        <v>0.0001740846705131693</v>
       </c>
       <c r="N7" t="n">
-        <v>0.005007952269190763</v>
+        <v>0.002535626899291876</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0002690199688348382</v>
+        <v>0.000565123406964202</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0008648124961662118</v>
+        <v>8.517998674688054e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001289906965969495</v>
+        <v>0.003767859341168656</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.0001428432831207693</v>
+        <v>0.0001096624142208847</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0008530160593598125</v>
+        <v>7.022107033067271e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>-8.677123387862973e-05</v>
+        <v>-0.0003725758465652596</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0005379293516762028</v>
+        <v>0.0005731101597462763</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001226308395196457</v>
+        <v>0.0001716824800001349</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001391863330614668</v>
+        <v>-0.0003698602376200899</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0005354226179306421</v>
+        <v>0.001241338545607967</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.210180623974273e-05</v>
+        <v>0.0003119294485787738</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002916982125427165</v>
+        <v>0.003663636100309237</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002750456855839039</v>
+        <v>0.005605690972149874</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.0001040943789035464</v>
+        <v>0.0005359739092245075</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.004594991968363e-05</v>
+        <v>0.001136364896677378</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.007498549703097834</v>
+        <v>0.005066525706949421</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.00601767225388688</v>
+        <v>0.006689029518269113</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0002395013598177676</v>
+        <v>-5.05368609529766e-05</v>
       </c>
       <c r="AG7" t="n">
-        <v>8.434937892086712e-05</v>
+        <v>-0.0004142904102727329</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0002980736381569649</v>
+        <v>0.0001312663335816089</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0004669071864410068</v>
+        <v>0.001877647672220889</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.004252747111950772</v>
+        <v>0.002793634871312578</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.00935253019675486</v>
+        <v>0.011001121248992</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0001021050841501337</v>
+        <v>0.0003941885025346869</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.004137487606098061</v>
+        <v>0.0009733399565396649</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0002031253193794713</v>
+        <v>0.0008474631563288593</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0003804304013246773</v>
+        <v>-0.00138967086742614</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.0002200077627670993</v>
+        <v>0.0003328041700646822</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.001231988227928932</v>
+        <v>4.230519535519114e-05</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.005258317629296588</v>
+        <v>0.005781115804143322</v>
       </c>
       <c r="AS7" t="n">
-        <v>-3.521990263655184e-05</v>
+        <v>0.0003020461922336515</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.0004812047475782844</v>
+        <v>-1.489631452824547e-05</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.0004606866821770805</v>
+        <v>3.410550380038569e-05</v>
       </c>
       <c r="AV7" t="n">
-        <v>-3.730700797797694e-05</v>
+        <v>-8.726003490403534e-05</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0002402237031712218</v>
+        <v>0.0001886975888077902</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.000240799778766787</v>
+        <v>0.0001214735515007614</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.0006860916567343389</v>
+        <v>0.0006224956420121108</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.001231236420963733</v>
+        <v>1.688727666015466e-05</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.000547343375788506</v>
+        <v>0.002342735441171917</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.002514963379781071</v>
+        <v>0.003285534775426974</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0001147063461376496</v>
+        <v>1.609269391696366e-05</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.74520069807893e-05</v>
+        <v>0.0001722884592762042</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0009711924757253077</v>
+        <v>-0.0002264168356899188</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0007289135716764816</v>
+        <v>0.0001929473301417794</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.0002054820655422673</v>
+        <v>0.0002886730094393664</v>
       </c>
       <c r="BH7" t="n">
-        <v>6.835269993166747e-05</v>
+        <v>0.0004558069976650258</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.002641612803388732</v>
+        <v>0.00266674797139968</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0004867002626883943</v>
+        <v>0.0005751900598850613</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.00140567155989329</v>
+        <v>0.0006027821114201082</v>
       </c>
       <c r="BL7" t="n">
-        <v>-8.536805743794006e-05</v>
+        <v>0.0002211688148075874</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.0005328185822875587</v>
+        <v>0.001080667525637336</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.00121855217374976</v>
+        <v>-0.0002608205280941855</v>
       </c>
       <c r="BO7" t="n">
-        <v>-3.924764104894511e-05</v>
+        <v>0.001401730247633431</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0004161374094939219</v>
+        <v>0.0007087388875224032</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0008386175224440906</v>
+        <v>0.0006554895806617555</v>
       </c>
       <c r="BS7" t="n">
-        <v>4.3300676421143e-05</v>
+        <v>0.0009994836043256405</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0002215440433330551</v>
+        <v>0.0006721453829089453</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.0006268310376858655</v>
+        <v>-0.000121752273544784</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.0002929571147228527</v>
+        <v>0.0001534470415702316</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.0003107178077045136</v>
+        <v>0.0007574902942104444</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.001843433508557346</v>
+        <v>0.0005240606291966154</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.851147086752495e-05</v>
+        <v>-0.0001086669331549384</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.735508503989403e-05</v>
+        <v>3.364985814662824e-05</v>
       </c>
       <c r="CB7" t="n">
-        <v>-6.281846168137989e-06</v>
+        <v>0.0002125959841655866</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0007627588801767559</v>
+        <v>0.0007321950064458238</v>
       </c>
       <c r="CD7" t="n">
-        <v>-0.0001909059354391174</v>
+        <v>-0.001308168476287519</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.0002825351261818987</v>
+        <v>2.669100570062963e-07</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.0002634559890670795</v>
+        <v>0.0003389996176635268</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.0001786205325225276</v>
+        <v>0.0005272000229173234</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0004137545195687764</v>
+        <v>6.980802792319607e-05</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.0003206222500060141</v>
+        <v>0.000258991725313712</v>
       </c>
       <c r="CJ7" t="n">
         <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0.0001031317448657254</v>
+        <v>-3.818323237560483e-05</v>
       </c>
       <c r="CL7" t="n">
-        <v>-7.102180050173602e-05</v>
+        <v>5.206525511974314e-05</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.0003674378218519847</v>
+        <v>0.000329152281101841</v>
       </c>
       <c r="CN7" t="n">
-        <v>8.604356988285434e-05</v>
+        <v>0.0002707626220388837</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0005943444747944838</v>
+        <v>0.0001527183303913882</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>3.480709202071664e-05</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0006755280818718623</v>
+        <v>0.0006237101084051843</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.000138792505204699</v>
+        <v>0.0005522939953682193</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.0001550004890339685</v>
+        <v>-0.0003275450945197766</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0.0008132792797039545</v>
+        <v>-0.0003646729866074283</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-5.186721991701226e-05</v>
       </c>
       <c r="CV7" t="n">
-        <v>-1.728907330567075e-05</v>
+        <v>1.735508503991623e-05</v>
       </c>
       <c r="CW7" t="n">
         <v>0</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.0003940029755290231</v>
+        <v>-0.0002138090948250515</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.0009354460473915471</v>
+        <v>-1.925573543374857e-05</v>
       </c>
       <c r="CZ7" t="n">
         <v>0</v>
       </c>
       <c r="DA7" t="n">
-        <v>0</v>
+        <v>8.652424891713029e-05</v>
       </c>
       <c r="DB7" t="n">
-        <v>-0.0001635578385436432</v>
+        <v>0.0006613347483936383</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.0003122831367105838</v>
+        <v>0.0001385134847681269</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0.0002325255175714414</v>
+        <v>3.120238584096159e-05</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.0002757975385202782</v>
+        <v>0.0003995770005689736</v>
       </c>
       <c r="DF7" t="n">
-        <v>-5.439433114860502e-05</v>
+        <v>-8.791808685836846e-05</v>
       </c>
       <c r="DG7" t="n">
-        <v>-0.0001348474909054098</v>
+        <v>-0.0008142365558807263</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.000716108779790292</v>
+        <v>-0.0003184546895551365</v>
       </c>
       <c r="DI7" t="n">
-        <v>-8.793351839490037e-05</v>
+        <v>-0.0001884917011473863</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.0002534075369989564</v>
+        <v>0.00108516433345679</v>
       </c>
       <c r="DK7" t="n">
-        <v>8.644536652837043e-05</v>
+        <v>-0.0003540392661731562</v>
       </c>
       <c r="DL7" t="n">
-        <v>-3.3170780008418e-05</v>
+        <v>-5.033557046978388e-05</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.0001561475902446097</v>
+        <v>-1.745200698082816e-05</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.0006778175359655914</v>
+        <v>-0.0003112395840399129</v>
       </c>
       <c r="DO7" t="n">
-        <v>-1.508473377800356e-05</v>
+        <v>-1.700698681659785e-05</v>
       </c>
       <c r="DP7" t="n">
-        <v>1.495289452687064e-05</v>
+        <v>0.0003992131685710776</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-3.457814661134151e-05</v>
+        <v>-3.490401396161191e-05</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>-0.0007178899320863408</v>
+        <v>-0.0005689155934658407</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.000172712003835801</v>
+        <v>0.000296307004973817</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>3.355704697987627e-05</v>
+        <v>1.677852348993536e-05</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0004163013435540208</v>
+        <v>-0.0002071452051363609</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.0001006606794984266</v>
+        <v>0.0005202317883974904</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0</v>
+        <v>0.0001019056890034731</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.0002547179328469429</v>
+        <v>0.0006653596572472442</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.0007728745948641369</v>
+        <v>-0.0003463009706273056</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0001552067940039981</v>
+        <v>3.46981263011803e-05</v>
       </c>
       <c r="ED7" t="n">
-        <v>-3.417634996584762e-05</v>
+        <v>0.0001045324911023437</v>
       </c>
       <c r="EE7" t="n">
-        <v>3.46981263011692e-05</v>
+        <v>5.174806710305236e-05</v>
       </c>
       <c r="EF7" t="n">
-        <v>3.364985814665045e-05</v>
+        <v>-0.0002896684905053126</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.0001332323375675293</v>
+        <v>0.0002239724919516018</v>
       </c>
       <c r="EH7" t="n">
-        <v>1.72890733056763e-05</v>
+        <v>-5.551115123125783e-18</v>
       </c>
       <c r="EI7" t="n">
-        <v>3.457856004928095e-05</v>
+        <v>5.178630128409023e-05</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.0002611624417307889</v>
+        <v>0.000230275120167206</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.0001548371275168825</v>
+        <v>0.0002033693186827168</v>
       </c>
       <c r="EL7" t="n">
         <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>5.033557046981163e-05</v>
+        <v>3.38723682287434e-05</v>
       </c>
       <c r="EN7" t="n">
-        <v>-0.0002436840800713269</v>
+        <v>0</v>
       </c>
       <c r="EO7" t="n">
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>5.204718945177045e-05</v>
+        <v>0.000189376213071335</v>
       </c>
       <c r="EQ7" t="n">
-        <v>5.206525511973203e-05</v>
+        <v>0.0004318135187343641</v>
       </c>
       <c r="ER7" t="n">
         <v>0</v>
@@ -3996,22 +3996,22 @@
         <v>0</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.0002168037648981436</v>
+        <v>0.0001005380877655615</v>
       </c>
       <c r="EU7" t="n">
-        <v>9.995481645562743e-05</v>
+        <v>-0.00030600720044337</v>
       </c>
       <c r="EV7" t="n">
-        <v>6.437077566784355e-05</v>
+        <v>4.926108374384563e-05</v>
       </c>
       <c r="EW7" t="n">
-        <v>1.734906315057905e-05</v>
+        <v>-0.0004129426379054557</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0001518026127142968</v>
+        <v>3.574167897190116e-05</v>
       </c>
       <c r="EY7" t="n">
-        <v>-3.490401396161746e-05</v>
+        <v>0.0001354667938913867</v>
       </c>
     </row>
     <row r="8">
@@ -4021,466 +4021,466 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001973970482241735</v>
+        <v>0.003262182337881422</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0006788883540145118</v>
+        <v>0.001635167198896576</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001232581747919948</v>
+        <v>0.0004356484398194915</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0002674756838113385</v>
+        <v>0.0002482807830591043</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0004181806372929225</v>
+        <v>0.000605394723504013</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003083190504357061</v>
+        <v>0.003432131832368698</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001233960849335594</v>
+        <v>0.0009774940358499352</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002731582974406593</v>
+        <v>0.001209403230380171</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002256768620763425</v>
+        <v>0.001900913891688322</v>
       </c>
       <c r="K8" t="n">
-        <v>0.000137910789799886</v>
+        <v>0.0005015151493329428</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002671169850556515</v>
+        <v>0.0001967749004711444</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001988074966698209</v>
+        <v>0.001268120417866952</v>
       </c>
       <c r="N8" t="n">
-        <v>0.008033509402857929</v>
+        <v>0.002864337801336764</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001525697736397905</v>
+        <v>0.002794937107601389</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002340855357739075</v>
+        <v>0.0008068134191533682</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.005478931903495588</v>
+        <v>0.007892507824937455</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001078991304922824</v>
+        <v>0.001618396502269653</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00113931782002322</v>
+        <v>0.001931234747597663</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0001882795763049977</v>
+        <v>0.0003186371205622679</v>
       </c>
       <c r="U8" t="n">
-        <v>8.326672684688675e-18</v>
+        <v>0.001767404901669287</v>
       </c>
       <c r="V8" t="n">
-        <v>0.004200014031764393</v>
+        <v>0.002186435533371567</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0020643761206323</v>
+        <v>0.0006625215181353338</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002777409969473865</v>
+        <v>0.002193899987661832</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001880569285168554</v>
+        <v>0.0007997900618243042</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003455917384420942</v>
+        <v>0.007814579764679525</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0063912816000811</v>
+        <v>0.009842609836372815</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001021498764304205</v>
+        <v>0.000836329461324678</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.001635758840222848</v>
+        <v>0.002939136462979516</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.008873558887317751</v>
+        <v>0.01097425887243294</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0076402881376194</v>
+        <v>0.008939562129254902</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.001574903328093777</v>
+        <v>0.001882102562551505</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0008246486950351461</v>
+        <v>0.0007400533134533371</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.000439665979358092</v>
+        <v>0.0004001227485658121</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.001218962857844508</v>
+        <v>0.003240671318656632</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.007563109375958207</v>
+        <v>0.006801817486405792</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.01357113737291865</v>
+        <v>0.01310515813645712</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0003961757541602273</v>
+        <v>0.001358740124408917</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.006523499833437779</v>
+        <v>0.005449782784260293</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.003398311261066358</v>
+        <v>0.002551128672005026</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.001106410304179131</v>
+        <v>0.0003257429649033388</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0002685509041008893</v>
+        <v>0.0008809964624590827</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.004560919497499305</v>
+        <v>0.003205873940025888</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.007132343784362363</v>
+        <v>0.008475849368071988</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0006639048009523169</v>
+        <v>0.001197148587228569</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0008861462423282451</v>
+        <v>0.000806611089270598</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.0008888663397392498</v>
+        <v>0.0003443360852103978</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.001844051797360044</v>
+        <v>0.0003029563847161132</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0007852524684633988</v>
+        <v>0.0008877385551444821</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0008192911430162569</v>
+        <v>0.0004948540240352212</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.003272956314546172</v>
+        <v>0.001459824530800063</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.002379728300954423</v>
+        <v>0.002793310572197472</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.00472756452419161</v>
+        <v>0.003380808443055516</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.008653940756878316</v>
+        <v>0.007425132462811265</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0002789747521172836</v>
+        <v>0.0001236477956283788</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0002074602903079759</v>
+        <v>0.0007320923427650006</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.002156146926928943</v>
+        <v>0.001664628797889276</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.004577775439150356</v>
+        <v>0.007967831326655692</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.002569194540452474</v>
+        <v>0.001022098748777478</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.001248030107669104</v>
+        <v>0.001139112485416865</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.004593709281426764</v>
+        <v>0.005844573973297526</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.001204231496538838</v>
+        <v>0.001803056982808313</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.003104610798384841</v>
+        <v>0.002195685456454496</v>
       </c>
       <c r="BL8" t="n">
-        <v>6.944419592530282e-05</v>
+        <v>0.001282396282668347</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.002617603617430311</v>
+        <v>0.001851907806065445</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.006969139226871382</v>
+        <v>0.003025243477822112</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.001643648893235758</v>
+        <v>0.004292560694724584</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0007000534961018102</v>
+        <v>0.001930822862868556</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.001568658711071627</v>
+        <v>0.002753366066976085</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.0006098637687617343</v>
+        <v>0.001274692045633915</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.001394368288037751</v>
+        <v>0.001118511826662283</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.002323245936000223</v>
+        <v>0.001274247531053316</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.001193998383639619</v>
+        <v>0.0006400778742184088</v>
       </c>
       <c r="BW8" t="n">
-        <v>2.413904087544549e-05</v>
+        <v>6.079125861014889e-05</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.001079329323134576</v>
+        <v>0.001167553247408595</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.004397328641572213</v>
+        <v>0.0009470636589365034</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.00154555523355332</v>
+        <v>0.002144831379320011</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0003126546774459837</v>
+        <v>0.0006048826551286024</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0006883226448211571</v>
+        <v>0.00180406685391121</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.001769120789011003</v>
+        <v>0.002015584872600659</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.0003086786456860751</v>
+        <v>0.0002670226712287893</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.00119361740935324</v>
+        <v>0.000348385677992108</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0005158228664276538</v>
+        <v>0.001238356947820268</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0008071946837383187</v>
+        <v>0.001629576453697049</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0007367652803732972</v>
+        <v>0.0008896425701548027</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.000685477683962063</v>
+        <v>0.00135830264094583</v>
       </c>
       <c r="CJ8" t="n">
         <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0004532478937979229</v>
+        <v>0.0007037756070135709</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0003661833151061916</v>
+        <v>0.000448830928884586</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.0009315782862386324</v>
+        <v>0.0006334026151700867</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.000261625688966699</v>
+        <v>0.001031937017596096</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.000921949354456178</v>
+        <v>0.0005460781782460982</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0001561725129765046</v>
+        <v>0.0003081039781487216</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.001278717331610973</v>
+        <v>0.001308173922112843</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.001492557576095158</v>
+        <v>0.002359365676992076</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.0005192217243854935</v>
+        <v>0.001347686310775908</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.0003294073889652971</v>
+        <v>0.0006591444200325536</v>
       </c>
       <c r="CU8" t="n">
-        <v>2.56322624743649e-05</v>
+        <v>5.204718945177045e-05</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.516778523491137e-05</v>
+        <v>0.0001244557774461974</v>
       </c>
       <c r="CW8" t="n">
         <v>0</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.001085586776589953</v>
+        <v>-0.0001715490249716151</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.002009618427820806</v>
+        <v>0.001163893893456627</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0002063674337945631</v>
+        <v>0.0001616621498927634</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0001823195788264703</v>
+        <v>0.0001468732148484142</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0003079875147779049</v>
+        <v>0.001617379953082088</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.00224759142468495</v>
+        <v>0.0007267578529818158</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0001561415683552697</v>
+        <v>0.0003204756550359317</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0007469284860903341</v>
+        <v>0.001152182882125916</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0003558465128338046</v>
+        <v>0.0005464944655994508</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0002084064033903182</v>
+        <v>-0.0001725893855725663</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.001230778279767539</v>
+        <v>0.001435193982693481</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0003409330154540341</v>
+        <v>0.0005638323012017333</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0004160175765445945</v>
+        <v>0.002197466639686163</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.0006148318633824118</v>
+        <v>0.0001645617747214556</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0005413738818574876</v>
+        <v>0.0007600113135503184</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.001443407610672143</v>
+        <v>0.0001438476579873976</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.000534681971700443</v>
+        <v>0.0007678427994703751</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.001482420718340144</v>
+        <v>0.000939288163412172</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0001561867325252431</v>
+        <v>8.674241933245841e-05</v>
       </c>
       <c r="DR8" t="n">
-        <v>2.512562814070418e-05</v>
+        <v>2.602359472588523e-05</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>2.617801047120061e-05</v>
       </c>
       <c r="DT8" t="n">
-        <v>4.428576646332282e-05</v>
+        <v>0.0001040314926381292</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.001033190559770816</v>
+        <v>0.001114733525866055</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0002083431735523528</v>
+        <v>0.0001532869405125287</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.0009039297807566433</v>
+        <v>0.0003842949476877827</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.0007671313265862124</v>
+        <v>0.001147519777740094</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.235602094238456e-05</v>
+        <v>0.0003525148715030263</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0008986912960712968</v>
+        <v>0.001404405824460722</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.001200211871809981</v>
+        <v>0.0005527638190954808</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0004288239526689275</v>
+        <v>0.0003387149241010134</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0003440440419980234</v>
+        <v>0.000656423478649798</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.0002585702748615027</v>
+        <v>0.0001720642823542645</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0002256010507955819</v>
+        <v>0.0006275001725822544</v>
       </c>
       <c r="EG8" t="n">
-        <v>-8.326672684688674e-18</v>
+        <v>0.0007154411561445279</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0002881654574898418</v>
+        <v>0.0001943793692858936</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0002157292304400593</v>
+        <v>0.001283336582286759</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0002655294496298671</v>
+        <v>0.001240923761928969</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0007059415333931341</v>
+        <v>0.001065233212400321</v>
       </c>
       <c r="EL8" t="n">
-        <v>5.186721991702891e-05</v>
+        <v>2.463054187192282e-05</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.0003969455419008422</v>
+        <v>9.285241885529927e-05</v>
       </c>
       <c r="EN8" t="n">
-        <v>-6.949919643257642e-05</v>
+        <v>0.0002444160241259596</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0005177457007133262</v>
+        <v>0.0006283633004384032</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0002983526081709848</v>
+        <v>0.001000548269520682</v>
       </c>
       <c r="ER8" t="n">
-        <v>0</v>
+        <v>2.617801047120061e-05</v>
       </c>
       <c r="ES8" t="n">
-        <v>0</v>
+        <v>6.843890945654185e-05</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0004269339748216583</v>
+        <v>0.000882372631960851</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0002855581729875989</v>
+        <v>-4.338771259979057e-05</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.000194229394673609</v>
+        <v>0.000268306503588156</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0006389308595991961</v>
+        <v>0.0006365721223567766</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0005647931957487084</v>
+        <v>0.0004970395655758325</v>
       </c>
       <c r="EY8" t="n">
-        <v>8.611713113611252e-05</v>
+        <v>0.000260544778749483</v>
       </c>
     </row>
     <row r="9">
@@ -4490,466 +4490,466 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.006197654941373499</v>
+        <v>0.01038525963149078</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002349533311876373</v>
+        <v>0.006147409076279376</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002550335570469797</v>
+        <v>0.001839000693962467</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001512713228194396</v>
+        <v>0.0008538587848932244</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0007633587786258667</v>
+        <v>0.001625172890733073</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005155993431855532</v>
+        <v>0.007856650585802894</v>
       </c>
       <c r="H9" t="n">
-        <v>0.006662375281622157</v>
+        <v>0.002082610204789992</v>
       </c>
       <c r="I9" t="n">
-        <v>0.006934673366834132</v>
+        <v>0.005738255033557104</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01128978224455609</v>
+        <v>0.007980295566502416</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0002776813606386597</v>
+        <v>0.00246356696738369</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009681881051176622</v>
+        <v>0.0004886561954624113</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003859060402684578</v>
+        <v>0.003712699514226181</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02070351758793968</v>
+        <v>0.01554438860971525</v>
       </c>
       <c r="O9" t="n">
-        <v>0.006073825503355712</v>
+        <v>0.006791116832957844</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003584589614740352</v>
+        <v>0.001641541038526006</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01838926174496645</v>
+        <v>0.01822880771881461</v>
       </c>
       <c r="R9" t="n">
-        <v>0.00242886884108251</v>
+        <v>0.003218390804597682</v>
       </c>
       <c r="S9" t="n">
-        <v>0.008509212730318239</v>
+        <v>0.004538139684583209</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001206030150753756</v>
+        <v>0.0006437077566784799</v>
       </c>
       <c r="U9" t="n">
-        <v>0.003908045977011521</v>
+        <v>0.003926174496644353</v>
       </c>
       <c r="V9" t="n">
-        <v>0.008561313163823603</v>
+        <v>0.00421628580624398</v>
       </c>
       <c r="W9" t="n">
-        <v>0.006577181208053706</v>
+        <v>0.005551700208188725</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03537174122948181</v>
+        <v>0.01103958802703573</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0003122831367105561</v>
+        <v>0.002274293590627174</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.004857621440536008</v>
+        <v>0.009407305306685043</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02410509031198689</v>
+        <v>0.02446633825944168</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002697095435684749</v>
+        <v>0.002785234899328881</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.002583892617449668</v>
+        <v>0.004170771756978608</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.02690698422915995</v>
+        <v>0.01486964917927261</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.02132635253054099</v>
+        <v>0.0196858638743455</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01036649214659684</v>
+        <v>0.006974323386537085</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.003008298755186822</v>
+        <v>0.001694329183955778</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0009011908593498541</v>
+        <v>0.001313628899835773</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.001912751677852365</v>
+        <v>0.009476223294279829</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.01828591256072167</v>
+        <v>0.01078838174273866</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.03994206630189893</v>
+        <v>0.02810720268006701</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.001802381718699708</v>
+        <v>0.003514817367332901</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.01766143106457239</v>
+        <v>0.01297208538587847</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.005159128978224436</v>
+        <v>0.006960716747070972</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.01261667203089797</v>
+        <v>0.002143845089903218</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.001544898616028312</v>
+        <v>0.002239834596829804</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.00616415410385257</v>
+        <v>0.007290640394088643</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.02345549738219893</v>
+        <v>0.01291448516579401</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.002864499517219177</v>
+        <v>0.007167470709855262</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.002981574539363452</v>
+        <v>0.004228187919463144</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.00167539267015705</v>
+        <v>0.002653342522398361</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.003484087102177535</v>
+        <v>0.002766251728907432</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.002378559463986562</v>
+        <v>0.004893177119228098</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.001158673962021262</v>
+        <v>0.001190859349855178</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.005214032829095594</v>
+        <v>0.003192227619708477</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.022248322147651</v>
+        <v>0.0053355704697987</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.01087027914614124</v>
+        <v>0.01116584564860422</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.03073704538139684</v>
+        <v>0.01426602343211576</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.00159059474412182</v>
+        <v>0.0003355704697987072</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.000416377515614097</v>
+        <v>0.003376981392143363</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.004280656581911802</v>
+        <v>0.005536912751677914</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0135234899328859</v>
+        <v>0.009819376026272553</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.007751677852349015</v>
+        <v>0.00259441707717567</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.002092050209204999</v>
+        <v>0.004755341144038572</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0142281879194631</v>
+        <v>0.01355704697986582</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.003221476510067112</v>
+        <v>0.005065926439972212</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.004377212745413561</v>
+        <v>0.004505954296749271</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001308724832214758</v>
+        <v>0.004198473282442705</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.003508207273897634</v>
+        <v>0.003282909559060188</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.02087248322147651</v>
+        <v>0.008604269293924438</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.007060755336617419</v>
+        <v>0.008959338387319094</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.001346469622331714</v>
+        <v>0.005065472088214984</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.003389261744966454</v>
+        <v>0.01385251550654719</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.001791867677463843</v>
+        <v>0.005961405926946916</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.004696223316912995</v>
+        <v>0.004376292212267397</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.00344589937973816</v>
+        <v>0.004053601340033497</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.003457814661134262</v>
+        <v>0.002986577181208094</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0003101309441764344</v>
+        <v>0.0003540392661731673</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.002080536912751685</v>
+        <v>0.002558782849239349</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.006561954624781818</v>
+        <v>0.003042876901798142</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.004502617801047082</v>
+        <v>0.004100620261888332</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.001476510067114101</v>
+        <v>0.002455048409405347</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.001306532663316584</v>
+        <v>0.002741151977793133</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.002824302134646961</v>
+        <v>0.002430213464696196</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.002178423236514626</v>
+        <v>0.002800829875518773</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.003141361256544473</v>
+        <v>0.003255033557047038</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.002081887578070707</v>
+        <v>0.002627939142462054</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.003182579564489085</v>
+        <v>0.003122831367106116</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.002348993288590606</v>
+        <v>0.002955665024630527</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.001247947454844034</v>
+        <v>0.004824259131633324</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0004479669193659608</v>
+        <v>6.568144499179418e-05</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.002627257799671612</v>
+        <v>0.001255230125523021</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.001440536013400318</v>
+        <v>0.007305306685044788</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.002274293590627185</v>
+        <v>0.0007046979865772296</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.001512713228194396</v>
+        <v>0.001550654720882172</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.001214855952794136</v>
+        <v>0.002558782849239383</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0003122831367105338</v>
+        <v>0.0008644536652835377</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.002814070351758757</v>
+        <v>0.002359472588480149</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.004216285806243947</v>
+        <v>0.00357390700902146</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.002703572578049551</v>
+        <v>0.004011065006915726</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.0007724493080141559</v>
+        <v>0.002144053601340046</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.000689179875947632</v>
+        <v>0.001342281879194696</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0006835269993165083</v>
+        <v>0.0009368494101318015</v>
       </c>
       <c r="CW9" t="n">
         <v>0</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.002594417077175715</v>
+        <v>0.002929014472777402</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.00273167358229609</v>
+        <v>0.005759888965995818</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.001208053691275179</v>
+        <v>0.0002775850104094424</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0004495159059475174</v>
+        <v>0.0001728907330567075</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0009424083769633218</v>
+        <v>0.002524204702628019</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.004328097731239056</v>
+        <v>0.00221476510067119</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.000899031811894968</v>
+        <v>0.000867453157529463</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.003365718251214378</v>
+        <v>0.004633471645919873</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.001291448516579374</v>
+        <v>0.001244813278008294</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.001029932410685552</v>
+        <v>0.001353226925745954</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.001842546063651551</v>
+        <v>0.004198473282442705</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.004149377593361092</v>
+        <v>0.001677852348993358</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0009045226130653394</v>
+        <v>0.003976486860304385</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.001937602627257828</v>
+        <v>0.002185981956974248</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0001708817498291104</v>
+        <v>0.0002627257799671545</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.00231543624161078</v>
+        <v>0.001912751677852398</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.003618090452261291</v>
+        <v>0.005636237897648777</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.00115183246073296</v>
+        <v>0.003630705394190969</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.004045643153527068</v>
+        <v>0.00246356696738369</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.00032185387833924</v>
+        <v>0.001171605789110974</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.000289668490505346</v>
+        <v>0.0002074688796680491</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0007925568573397768</v>
+        <v>0.0002734107997265589</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.001577181208053713</v>
+        <v>0.0008027923211168852</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.00128383067314356</v>
+        <v>0.001873698820263647</v>
       </c>
       <c r="DV9" t="n">
-        <v>6.915629322270522e-05</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0005149662053427706</v>
+        <v>0.002914642609299034</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.00406040268456378</v>
+        <v>0.001978479694550484</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.004489112227805681</v>
+        <v>0.007883817427385975</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.001037344398340345</v>
+        <v>0.0009303928325293031</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.001541038525963123</v>
+        <v>0.002074688796680546</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.002881072026800635</v>
+        <v>0.003665283540802311</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.003959731543624179</v>
+        <v>0.001590594744121743</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.001239530988274717</v>
+        <v>0.001677852348993336</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0004597701149425592</v>
+        <v>0.0006030150753769004</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.001383125864453771</v>
+        <v>0.002047900034710159</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.001442953020134241</v>
+        <v>0.002186740715029489</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0005471515931766979</v>
+        <v>0.0009045226130653505</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.001901798063623894</v>
+        <v>0.00163137799375217</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.002445561139028429</v>
+        <v>0.001839080459770104</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.001442953020134219</v>
+        <v>0.001946308724832257</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0001642036124794855</v>
+        <v>0.000172294968986908</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0005551700208187738</v>
+        <v>0.00086147484493454</v>
       </c>
       <c r="EN9" t="n">
-        <v>3.350083752093891e-05</v>
+        <v>0.000675893144512374</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.001378359751895264</v>
+        <v>0.001174496644295353</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.002080536912751674</v>
+        <v>0.002074688796680546</v>
       </c>
       <c r="ER9" t="n">
-        <v>0</v>
+        <v>0.0009011908593498541</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0002067539627842896</v>
+        <v>0.0002684563758389658</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.000838926174496657</v>
+        <v>0.001442953020134286</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.001012216404886523</v>
+        <v>0.0002792321116928065</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0005898681471199652</v>
+        <v>0.0006245662734212232</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.002455048409405358</v>
+        <v>0.001596113809854194</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.002420470262794017</v>
+        <v>0.0009395973154363135</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0005369127516778871</v>
+        <v>0.0005858028945554872</v>
       </c>
     </row>
   </sheetData>
